--- a/data/trans_orig/P44D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1761,97 +1761,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2104,97 +2104,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>35,66%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>3062</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9531</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>9320</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>35,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10071</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>22019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79116</t>
+          <t>77998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>97219</t>
+          <t>96902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>173900</t>
+          <t>172875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198101</t>
+          <t>198707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2016 (tasa de respuesta: 93,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>61836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70389</t>
+          <t>70354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4739,97 +4739,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>46815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124505</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142780</t>
+          <t>143002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87493</t>
+          <t>86315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100917</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217413</t>
+          <t>218338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240394</t>
+          <t>240829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20386</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55140</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91871</t>
+          <t>92973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108804</t>
+          <t>109027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>62641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147712</t>
+          <t>148793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167474</t>
+          <t>167827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62107</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>74307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37542</t>
+          <t>38050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45255</t>
+          <t>45276</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102001</t>
+          <t>103193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117433</t>
+          <t>117756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,82 +6703,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7041</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>26141</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3856</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>7041</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>26943</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304877</t>
+          <t>302884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329425</t>
+          <t>329385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,82 +6816,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>31212</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27901</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32428</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>355606</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>336506</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>361947</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31212</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28733</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32425</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>88,17%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>355606</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>335704</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>361542</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149820</t>
+          <t>150064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158833</t>
+          <t>158841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77875</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83778</t>
+          <t>83793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231833</t>
+          <t>230906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241439</t>
+          <t>240965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -7374,97 +7374,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>391</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66214</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108993</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176220</t>
+          <t>176268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111249</t>
+          <t>111304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117883</t>
+          <t>117845</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114816</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121517</t>
+          <t>121611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79991</t>
+          <t>80460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>27372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43055</t>
+          <t>47148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115289</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>693155</t>
+          <t>692686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>754010</t>
+          <t>753035</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>428498</t>
+          <t>428507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>445453</t>
+          <t>445290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1130518</t>
+          <t>1132352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1202752</t>
+          <t>1198659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27178</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47851</t>
+          <t>45908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>79263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96902</t>
+          <t>96788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172875</t>
+          <t>174818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198707</t>
+          <t>198785</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24199</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>36501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41736</t>
+          <t>41642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61836</t>
+          <t>61798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>70373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>35264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>35264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46815</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143002</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>86315</t>
+          <t>86585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100916</t>
+          <t>101030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218338</t>
+          <t>216853</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240829</t>
+          <t>240060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>49124</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101153</t>
+          <t>106733</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92973</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109027</t>
+          <t>114785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57288</t>
+          <t>64963</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>58742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>70469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>158440</t>
+          <t>171696</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148793</t>
+          <t>160034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167827</t>
+          <t>181904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129190</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129190</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129190</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73663</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>202852</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202852</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202852</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>23352</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>70472</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>62901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74307</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41990</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45276</t>
+          <t>50849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>110652</t>
+          <t>118145</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103193</t>
+          <t>109205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117756</t>
+          <t>125652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>132343</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132343</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>132343</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>324395</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302884</t>
+          <t>80276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329385</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>355606</t>
+          <t>119449</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>336506</t>
+          <t>113563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>361947</t>
+          <t>123557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330058</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330058</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330058</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>362647</t>
+          <t>127458</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>362647</t>
+          <t>127458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>362647</t>
+          <t>127458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>156151</t>
+          <t>170939</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150064</t>
+          <t>166465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158841</t>
+          <t>173554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>81428</t>
+          <t>89279</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77925</t>
+          <t>85222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83793</t>
+          <t>91726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>237579</t>
+          <t>260219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230906</t>
+          <t>253296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240965</t>
+          <t>263982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159609</t>
+          <t>174257</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159609</t>
+          <t>174257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>159609</t>
+          <t>174257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>267779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>267779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>267779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>396</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>396</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -7517,27 +7517,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>110596</t>
+          <t>120224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109029</t>
+          <t>117699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7552,27 +7552,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>178203</t>
+          <t>194569</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176268</t>
+          <t>193111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>115230</t>
+          <t>127403</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111304</t>
+          <t>122841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117845</t>
+          <t>130010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>119115</t>
+          <t>131252</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114659</t>
+          <t>126844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>134041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>120383</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>55763</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80460</t>
+          <t>68898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>86210</t>
+          <t>93919</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>79003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113455</t>
+          <t>110229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>721853</t>
+          <t>511832</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>692686</t>
+          <t>498697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>753035</t>
+          <t>525460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>437744</t>
+          <t>483497</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>428507</t>
+          <t>474170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>445290</t>
+          <t>492430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1159597</t>
+          <t>995330</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1132352</t>
+          <t>979020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1198659</t>
+          <t>1010246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>773146</t>
+          <t>567595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>773146</t>
+          <t>567595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>773146</t>
+          <t>567595</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1245807</t>
+          <t>1089249</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1245807</t>
+          <t>1089249</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1245807</t>
+          <t>1089249</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
